--- a/data/trans_dic/IP12B$fiebre-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$fiebre-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,38</t>
+          <t>0,0; 29,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 37,58</t>
+          <t>4,87; 37,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 38,14</t>
+          <t>4,58; 42,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 50,23</t>
+          <t>0,19; 49,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 51,53</t>
+          <t>7,44; 52,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,37; 84,33</t>
+          <t>25,48; 77,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 32,17</t>
+          <t>3,77; 32,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,25; 36,77</t>
+          <t>10,37; 36,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,21; 50,13</t>
+          <t>15,43; 49,62</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,58</t>
+          <t>0,0; 20,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 33,04</t>
+          <t>3,32; 30,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 39,28</t>
+          <t>10,33; 38,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,12</t>
+          <t>0,0; 23,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,09; 34,81</t>
+          <t>8,51; 36,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,72; 42,76</t>
+          <t>9,59; 39,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 14,87</t>
+          <t>1,76; 13,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,38; 27,87</t>
+          <t>8,64; 27,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,47; 33,22</t>
+          <t>12,27; 32,91</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,13</t>
+          <t>0,0; 35,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,73</t>
+          <t>0,0; 29,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,22</t>
+          <t>0,0; 24,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,88</t>
+          <t>0,0; 36,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,88</t>
+          <t>0,0; 16,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 23,98</t>
+          <t>2,78; 24,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,22</t>
+          <t>0,0; 9,8</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,12</t>
+          <t>0,0; 37,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,99</t>
+          <t>0,0; 32,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 57,36</t>
+          <t>7,78; 56,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,31</t>
+          <t>0,0; 18,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 36,38</t>
+          <t>3,91; 35,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,42</t>
+          <t>0,0; 18,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,36</t>
+          <t>1,51; 13,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 21,85</t>
+          <t>6,89; 21,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,74; 22,62</t>
+          <t>7,51; 23,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,35; 20,06</t>
+          <t>5,35; 19,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,62; 27,04</t>
+          <t>8,93; 25,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,29; 26,81</t>
+          <t>9,32; 26,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 13,62</t>
+          <t>4,37; 14,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,37; 20,15</t>
+          <t>9,51; 20,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,97; 20,8</t>
+          <t>9,25; 20,59</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3125</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3511</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3899</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2657</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>6636</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5847</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2726</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>874; 6806</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>544; 5009</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>18; 4644</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>985; 6962</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1884; 5762</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>695; 5974</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3234; 11284</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2971; 9558</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2771</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5058</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4938</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3857</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7709</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>8915</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3364</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>673; 6218</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2347; 8723</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4578</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2138; 9184</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1750; 7222</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>630; 4836</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>3919; 12489</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>5027; 13483</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2291</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3789</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4186</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2941</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3733</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3466</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>674; 5942</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2555</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1888</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2486</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1398</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2966</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2990</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>607; 4387</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2728</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>616; 5660</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4517</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2564</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8010</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7570</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5233</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10024</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7756</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7798</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>18034</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>15325</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>663; 5848</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4221; 13253</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4141; 12848</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2498; 9219</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5674; 16080</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4462; 12443</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3959; 12714</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>11872; 25853</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>9521; 21208</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$fiebre-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$fiebre-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,85</t>
+          <t>0,0; 32,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 37,88</t>
+          <t>5,08; 39,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 42,21</t>
+          <t>4,5; 40,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 49,81</t>
+          <t>6,94; 52,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,44; 52,61</t>
+          <t>7,67; 52,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,48; 77,92</t>
+          <t>25,71; 78,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 32,37</t>
+          <t>3,72; 32,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,37; 36,17</t>
+          <t>9,5; 35,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,43; 49,62</t>
+          <t>15,13; 49,2</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,95</t>
+          <t>0,0; 21,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,32; 30,72</t>
+          <t>3,24; 30,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,33; 38,39</t>
+          <t>10,91; 40,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,33</t>
+          <t>0,0; 20,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 36,56</t>
+          <t>8,58; 34,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,59; 39,58</t>
+          <t>9,68; 39,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 13,55</t>
+          <t>1,78; 14,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 27,53</t>
+          <t>8,75; 27,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,27; 32,91</t>
+          <t>13,38; 32,88</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,27</t>
+          <t>0,0; 38,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,87</t>
+          <t>0,0; 33,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,45</t>
+          <t>0,0; 25,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,52</t>
+          <t>0,0; 36,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,74</t>
+          <t>0,0; 18,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 24,52</t>
+          <t>2,82; 25,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,8</t>
+          <t>0,0; 11,83</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,34</t>
+          <t>0,0; 39,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,96</t>
+          <t>0,0; 33,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,78; 56,29</t>
+          <t>7,75; 57,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,2</t>
+          <t>0,0; 27,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 35,96</t>
+          <t>3,9; 35,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,77</t>
+          <t>0,0; 20,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,33</t>
+          <t>1,51; 14,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,89; 21,62</t>
+          <t>6,78; 20,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,51; 23,31</t>
+          <t>7,36; 22,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,35; 19,74</t>
+          <t>5,49; 20,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,93; 25,3</t>
+          <t>8,06; 24,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,32; 26,0</t>
+          <t>9,11; 26,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 14,04</t>
+          <t>4,96; 14,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,51; 20,71</t>
+          <t>9,88; 20,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,25; 20,59</t>
+          <t>10,26; 20,5</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2726</t>
+          <t>0; 2956</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>874; 6806</t>
+          <t>912; 7033</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>544; 5009</t>
+          <t>534; 4825</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18; 4644</t>
+          <t>647; 4914</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>985; 6962</t>
+          <t>1016; 6911</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1884; 5762</t>
+          <t>1901; 5774</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>695; 5974</t>
+          <t>687; 5975</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3234; 11284</t>
+          <t>2965; 11078</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2971; 9558</t>
+          <t>2914; 9477</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3364</t>
+          <t>0; 3388</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>673; 6218</t>
+          <t>657; 6216</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2347; 8723</t>
+          <t>2479; 9226</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4578</t>
+          <t>0; 4037</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2138; 9184</t>
+          <t>2156; 8691</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1750; 7222</t>
+          <t>1767; 7177</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>630; 4836</t>
+          <t>634; 5275</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3919; 12489</t>
+          <t>3971; 12651</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5027; 13483</t>
+          <t>5482; 13471</t>
         </is>
       </c>
     </row>
@@ -1743,17 +1743,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3789</t>
+          <t>0; 4163</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4186</t>
+          <t>0; 4724</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2941</t>
+          <t>0; 3007</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3733</t>
+          <t>0; 3707</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1773,17 +1773,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3466</t>
+          <t>0; 3765</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>674; 5942</t>
+          <t>682; 6147</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2555</t>
+          <t>0; 3084</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2966</t>
+          <t>0; 3132</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2990</t>
+          <t>0; 3007</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>607; 4387</t>
+          <t>604; 4459</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2728</t>
+          <t>0; 4096</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>616; 5660</t>
+          <t>614; 5589</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4517</t>
+          <t>0; 4851</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>663; 5848</t>
+          <t>661; 6276</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4221; 13253</t>
+          <t>4156; 12806</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4141; 12848</t>
+          <t>4059; 12160</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2498; 9219</t>
+          <t>2566; 9752</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5674; 16080</t>
+          <t>5124; 15427</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4462; 12443</t>
+          <t>4358; 12783</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3959; 12714</t>
+          <t>4495; 12777</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11872; 25853</t>
+          <t>12336; 26100</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9521; 21208</t>
+          <t>10561; 21110</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$fiebre-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$fiebre-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21,83%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26,53%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>52,72%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>6,81%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>17,39%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>16,41%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21,83%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>26,53%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>52,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,38</t>
+          <t>6,9; 50,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 39,15</t>
+          <t>7,66; 51,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 40,66</t>
+          <t>19,37; 84,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 52,71</t>
+          <t>0,0; 34,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,67; 52,22</t>
+          <t>4,83; 37,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,71; 78,09</t>
+          <t>4,63; 38,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 32,38</t>
+          <t>3,68; 32,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,5; 35,51</t>
+          <t>10,25; 36,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,13; 49,2</t>
+          <t>16,21; 50,13</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19,66%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21,14%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>4,2%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>13,69%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>22,26%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>19,66%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>21,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,1</t>
+          <t>0,0; 20,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 30,71</t>
+          <t>9,09; 34,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,91; 40,6</t>
+          <t>9,72; 42,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,57</t>
+          <t>0,0; 21,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,58; 34,6</t>
+          <t>3,47; 33,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,68; 39,33</t>
+          <t>10,86; 39,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 14,79</t>
+          <t>1,78; 14,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,75; 27,89</t>
+          <t>9,38; 27,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,38; 32,88</t>
+          <t>13,47; 33,22</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,03%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,24%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>9,76%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,69%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,03%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,72</t>
+          <t>0,0; 43,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 32,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,26</t>
+          <t>0,0; 29,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 21,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,18</t>
+          <t>0,0; 16,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 25,36</t>
+          <t>2,75; 23,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,83</t>
+          <t>0,0; 11,22</t>
         </is>
       </c>
     </row>
@@ -955,27 +955,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24,22%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>7,53%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>8,23%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24,22%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,43</t>
+          <t>7,75; 57,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,13</t>
+          <t>0,0; 22,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 57,21</t>
+          <t>0,0; 38,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,33</t>
+          <t>0,0; 39,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 35,51</t>
+          <t>3,93; 36,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,16</t>
+          <t>0,0; 18,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11,2%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15,77%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16,21%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,84%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>13,07%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>13,73%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>15,77%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>16,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 14,3</t>
+          <t>5,35; 20,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,78; 20,89</t>
+          <t>9,62; 27,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,36; 22,06</t>
+          <t>9,29; 26,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 20,88</t>
+          <t>1,44; 13,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,06; 24,27</t>
+          <t>7,14; 21,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,11; 26,71</t>
+          <t>7,74; 22,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 14,11</t>
+          <t>4,38; 13,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,88; 20,91</t>
+          <t>9,37; 20,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,26; 20,5</t>
+          <t>9,97; 20,8</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3511</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3899</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>622</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>3125</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1947</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3511</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3899</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2956</t>
+          <t>644; 4683</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>912; 7033</t>
+          <t>1013; 6819</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>534; 4825</t>
+          <t>1432; 6236</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>647; 4914</t>
+          <t>0; 3139</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1016; 6911</t>
+          <t>867; 6752</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1901; 5774</t>
+          <t>549; 4526</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>687; 5975</t>
+          <t>679; 5937</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2965; 11078</t>
+          <t>3197; 11473</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2914; 9477</t>
+          <t>3121; 9656</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4938</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3857</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>674</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2771</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5058</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3857</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3388</t>
+          <t>0; 3948</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>657; 6216</t>
+          <t>2284; 8743</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2479; 9226</t>
+          <t>1774; 7803</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4037</t>
+          <t>0; 3465</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2156; 8691</t>
+          <t>702; 6688</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1767; 7177</t>
+          <t>2467; 8925</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>634; 5275</t>
+          <t>633; 5304</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3971; 12651</t>
+          <t>4257; 12639</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5482; 13471</t>
+          <t>5519; 13610</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>670</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1368</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>564</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4163</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4724</t>
+          <t>0; 4485</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3452</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3707</t>
+          <t>0; 4165</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2552</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3765</t>
+          <t>0; 3497</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>682; 6147</t>
+          <t>666; 5811</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3084</t>
+          <t>0; 2925</t>
         </is>
       </c>
     </row>
@@ -1800,22 +1800,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1853,27 +1853,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1888</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>746</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1888</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3132</t>
+          <t>604; 4470</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3007</t>
+          <t>0; 3343</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>604; 4459</t>
+          <t>0; 3029</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4096</t>
+          <t>0; 3628</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>614; 5589</t>
+          <t>618; 5725</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4851</t>
+          <t>0; 4433</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1963,27 +1963,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5233</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10024</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7756</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>2564</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>8010</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>7570</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>5233</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>10024</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7756</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>661; 6276</t>
+          <t>2501; 9368</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4156; 12806</t>
+          <t>6114; 17188</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4059; 12160</t>
+          <t>4446; 12831</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2566; 9752</t>
+          <t>632; 5862</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5124; 15427</t>
+          <t>4374; 13392</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4358; 12783</t>
+          <t>4268; 12467</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4495; 12777</t>
+          <t>3964; 12340</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12336; 26100</t>
+          <t>11696; 25154</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10561; 21110</t>
+          <t>10270; 21420</t>
         </is>
       </c>
     </row>
